--- a/AAII_Financials/Quarterly/BBDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>BBDO</t>
   </si>
@@ -656,215 +656,227 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4612300</v>
+      </c>
+      <c r="E8" s="3">
         <v>4867900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4140000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3975100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4090500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4009800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3477900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3859400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3321300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3573200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3714800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2943800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3579600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3626800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2619800</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E9" s="3">
         <v>46300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>54800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>57600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>52000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>59100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>62400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>69300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>75800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>69200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>68600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>62700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4563600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4821600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4085200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3918300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4032900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3957800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3418800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3797800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3258900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3503900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3639000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2874700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3511000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3564100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2555000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,102 +992,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>279000</v>
+      </c>
+      <c r="E14" s="3">
         <v>292800</v>
       </c>
-      <c r="E14" s="3">
-        <v>132900</v>
-      </c>
       <c r="F14" s="3">
+        <v>132600</v>
+      </c>
+      <c r="G14" s="3">
         <v>412200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>760200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>276600</v>
       </c>
-      <c r="I14" s="3">
-        <v>251100</v>
-      </c>
       <c r="J14" s="3">
+        <v>251300</v>
+      </c>
+      <c r="K14" s="3">
         <v>314100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>229600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>282400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>519800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>379200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>283800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>111900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>237700</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>204500</v>
+      </c>
+      <c r="E15" s="3">
         <v>206200</v>
       </c>
-      <c r="E15" s="3">
-        <v>263900</v>
-      </c>
       <c r="F15" s="3">
+        <v>198900</v>
+      </c>
+      <c r="G15" s="3">
         <v>199600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>207300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>171400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>201700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>229600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>222500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>241400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>229900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>250700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>255700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>332900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>209800</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,102 +1111,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3020400</v>
+      </c>
+      <c r="E17" s="3">
         <v>3160000</v>
       </c>
-      <c r="E17" s="3">
-        <v>3112900</v>
-      </c>
       <c r="F17" s="3">
+        <v>3113100</v>
+      </c>
+      <c r="G17" s="3">
         <v>2732300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2626600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2743400</v>
       </c>
-      <c r="I17" s="3">
-        <v>2730900</v>
-      </c>
       <c r="J17" s="3">
+        <v>2730600</v>
+      </c>
+      <c r="K17" s="3">
         <v>2589600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2504200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2525900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3545300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2256300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2800700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2353700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2998700</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1592000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1707900</v>
       </c>
-      <c r="E18" s="3">
-        <v>1027100</v>
-      </c>
       <c r="F18" s="3">
+        <v>1026900</v>
+      </c>
+      <c r="G18" s="3">
         <v>1242800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1463900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1266400</v>
       </c>
-      <c r="I18" s="3">
-        <v>747000</v>
-      </c>
       <c r="J18" s="3">
+        <v>747300</v>
+      </c>
+      <c r="K18" s="3">
         <v>1269800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>817000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1047300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>169500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>687500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>778900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1273100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-378900</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,102 +1231,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-85900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-150000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-85100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-90800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-67700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-36800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-68300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-84300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-92500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-107900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-103800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-137700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-78200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-68700</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1899800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2000000</v>
       </c>
-      <c r="E21" s="3">
-        <v>1441100</v>
-      </c>
       <c r="F21" s="3">
+        <v>1375800</v>
+      </c>
+      <c r="G21" s="3">
         <v>1527500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1762000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1505500</v>
       </c>
-      <c r="I21" s="3">
-        <v>985500</v>
-      </c>
       <c r="J21" s="3">
+        <v>985800</v>
+      </c>
+      <c r="K21" s="3">
         <v>1567800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1123800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1381200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>507300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1042000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1172300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1684200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100400</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,102 +1379,111 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1416200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1501000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1044300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>915700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>794600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1057500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>532800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1024000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>671700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>857400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-242400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>412100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>632800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1239400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-547900</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E24" s="3">
         <v>498300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-143400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-129000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-332200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>67500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-147700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>115900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-82200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-548700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-283000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-211600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>158300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-664300</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,102 +1529,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1398600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1002600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1187700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1044800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1126700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>989900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>680500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>908200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>753900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>838000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>306400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>695000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>844400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1081000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1378100</v>
+      </c>
+      <c r="E27" s="3">
         <v>992600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1180200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1032100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1113400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>977600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>670400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>894300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>741400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>821600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>295800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>680800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>833000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1066400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,102 +1829,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>103300</v>
+      </c>
+      <c r="E32" s="3">
         <v>85900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>150000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>85100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>90800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>67700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>36800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>68300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>84300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>92500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>107900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>103800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>137700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>78200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>68700</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1378100</v>
+      </c>
+      <c r="E33" s="3">
         <v>992600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1180200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1032100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1113400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>977600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>670400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>894300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>741400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>821600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>295800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>680800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>833000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1066400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,107 +1979,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1378100</v>
+      </c>
+      <c r="E35" s="3">
         <v>992600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1180200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1032100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1113400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>977600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>670400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>894300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>741400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>821600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>295800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>680800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>833000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1066400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,431 +2126,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5225500</v>
+      </c>
+      <c r="E41" s="3">
         <v>5277600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4657200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5227600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5083200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4916800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5954500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6350700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7559400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7732800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8560400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6062400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7682300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5717100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5400400</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>48880700</v>
+      </c>
+      <c r="E42" s="3">
         <v>62448400</v>
       </c>
-      <c r="E42" s="3">
-        <v>44516000</v>
-      </c>
       <c r="F42" s="3">
+        <v>99453500</v>
+      </c>
+      <c r="G42" s="3">
         <v>46323500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>43106200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>30932800</v>
       </c>
-      <c r="I42" s="3">
-        <v>32974500</v>
-      </c>
       <c r="J42" s="3">
+        <v>60127600</v>
+      </c>
+      <c r="K42" s="3">
         <v>39711000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>39817400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>46284600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>42399000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>49393000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>40340900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>40906900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>24515500</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1773900</v>
+        <v>4385400</v>
       </c>
       <c r="E43" s="3">
-        <v>1480800</v>
+        <v>4518000</v>
       </c>
       <c r="F43" s="3">
+        <v>3609100</v>
+      </c>
+      <c r="G43" s="3">
         <v>3630400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3875100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3804100</v>
       </c>
-      <c r="I43" s="3">
-        <v>2836300</v>
-      </c>
       <c r="J43" s="3">
+        <v>4367600</v>
+      </c>
+      <c r="K43" s="3">
         <v>2394200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2694200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2318900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4351700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2344000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1376000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1366400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4189200</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>899500</v>
+      </c>
+      <c r="E44" s="3">
         <v>737000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>682200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>698900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>682100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>639100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>565100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>647500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>624800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>270100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>273800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>250100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>269800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>250300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5871700</v>
+        <v>4616900</v>
       </c>
       <c r="E45" s="3">
-        <v>5378700</v>
+        <v>4557900</v>
       </c>
       <c r="F45" s="3">
+        <v>4322500</v>
+      </c>
+      <c r="G45" s="3">
         <v>4268600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4109900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3815600</v>
       </c>
-      <c r="I45" s="3">
-        <v>4071500</v>
-      </c>
       <c r="J45" s="3">
+        <v>3515500</v>
+      </c>
+      <c r="K45" s="3">
         <v>4476900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3867900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4270200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4284100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4142400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7267200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6750700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3870600</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>103446400</v>
+        <v>87168500</v>
       </c>
       <c r="E46" s="3">
-        <v>83294700</v>
+        <v>104876800</v>
       </c>
       <c r="F46" s="3">
+        <v>133868400</v>
+      </c>
+      <c r="G46" s="3">
         <v>87045500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>77782100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>63294100</v>
       </c>
-      <c r="I46" s="3">
-        <v>64729600</v>
-      </c>
       <c r="J46" s="3">
+        <v>92858100</v>
+      </c>
+      <c r="K46" s="3">
         <v>77554400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>74330400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>82415000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>83043700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>84313800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>78500000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>74360200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>56502700</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>174527500</v>
+        <v>188349800</v>
       </c>
       <c r="E47" s="3">
-        <v>171509200</v>
+        <v>173097100</v>
       </c>
       <c r="F47" s="3">
+        <v>74769100</v>
+      </c>
+      <c r="G47" s="3">
         <v>158623900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>150590300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>140230900</v>
       </c>
-      <c r="I47" s="3">
-        <v>128117600</v>
-      </c>
       <c r="J47" s="3">
+        <v>70221600</v>
+      </c>
+      <c r="K47" s="3">
         <v>139254400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>137760900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>150336200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>158658500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>143096900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>152938100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>136202700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>136535800</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1807400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1841700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1707600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1691200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1684400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1594400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1652500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1871900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2004000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2126900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2291300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2200300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2385000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2409700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2264400</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5190600</v>
+      </c>
+      <c r="E49" s="3">
         <v>5096100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4673100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4533900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4401500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4063900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3839900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4259500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4073300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4475700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4556000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3940200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4057100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3881100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3556100</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15768000</v>
+      </c>
+      <c r="E52" s="3">
         <v>11770700</v>
       </c>
-      <c r="E52" s="3">
-        <v>8862200</v>
-      </c>
       <c r="F52" s="3">
+        <v>9954100</v>
+      </c>
+      <c r="G52" s="3">
         <v>10509600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10883600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9773600</v>
       </c>
-      <c r="I52" s="3">
-        <v>8183000</v>
-      </c>
       <c r="J52" s="3">
+        <v>9128600</v>
+      </c>
+      <c r="K52" s="3">
         <v>11304000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11281200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10098300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6381000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9860300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8972300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8503800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7742800</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>476533800</v>
+      </c>
+      <c r="E54" s="3">
         <v>466794100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>423080500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>413325100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>394136300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>358358700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>334602700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>370547100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>360950100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>390006700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>397239100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>379459600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>386458800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>361159600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>339024900</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>151040000</v>
+      </c>
+      <c r="E57" s="3">
         <v>144189800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>132164700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>125172600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>117854100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>108573300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>104895200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>113260100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>111500700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>121566600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>128968300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>122930700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>123188000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>116365300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>112250400</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>132590100</v>
+      </c>
+      <c r="E58" s="3">
         <v>91959200</v>
       </c>
-      <c r="E58" s="3">
-        <v>83084200</v>
-      </c>
       <c r="F58" s="3">
+        <v>122151200</v>
+      </c>
+      <c r="G58" s="3">
         <v>84970400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>82803700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>76349900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>50425800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>75488800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>71892000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>74999700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>59632000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>71145200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>76431000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>74128500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>45905000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>91969500</v>
+      </c>
+      <c r="E59" s="3">
         <v>91792700</v>
       </c>
-      <c r="E59" s="3">
-        <v>81588400</v>
-      </c>
       <c r="F59" s="3">
+        <v>85902600</v>
+      </c>
+      <c r="G59" s="3">
         <v>79816800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>74955900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>68435500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7235100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8877500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>65045800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70039600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8005200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>66829200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>67926800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8282900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7895500</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>379160600</v>
+      </c>
+      <c r="E60" s="3">
         <v>331367900</v>
       </c>
-      <c r="E60" s="3">
-        <v>299091300</v>
-      </c>
       <c r="F60" s="3">
+        <v>342472500</v>
+      </c>
+      <c r="G60" s="3">
         <v>293141900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>279081000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>256307300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>164384700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>199159200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>249516500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>268267900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>198621200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>262301900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>268904300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>199657900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>167541500</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>29291500</v>
+      </c>
+      <c r="E61" s="3">
         <v>70796400</v>
       </c>
-      <c r="E61" s="3">
-        <v>65183200</v>
-      </c>
       <c r="F61" s="3">
+        <v>26116200</v>
+      </c>
+      <c r="G61" s="3">
         <v>59253200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54444500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45467800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>63686200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>50810400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>53498900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>59914800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>73795900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>56198600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>52689100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>47326900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>64801700</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32361300</v>
+      </c>
+      <c r="E62" s="3">
         <v>29667100</v>
       </c>
-      <c r="E62" s="3">
-        <v>25972900</v>
-      </c>
       <c r="F62" s="3">
+        <v>21658700</v>
+      </c>
+      <c r="G62" s="3">
         <v>27525800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28232600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26473700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>78947400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>89621300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28084200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28441300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>90071100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>27216800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29763600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>81508500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>76105500</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>441262000</v>
+      </c>
+      <c r="E66" s="3">
         <v>432234000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>390591600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>380273600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>362103200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>328525100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>307287400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>339757900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>331201700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>356809800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>362819500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>346042900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>351811400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>328959300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>308757600</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3534,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17034300</v>
+      </c>
+      <c r="E72" s="3">
         <v>16318100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16443900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16500100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15825000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14607200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13261700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14870000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14215900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15451100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15655400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15433200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15845700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14917100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13859800</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34991000</v>
+      </c>
+      <c r="E76" s="3">
         <v>34459100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32392000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>32955900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31943500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29737800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27229200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30692700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29655000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>33070400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34278800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>33285300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34521900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>32089700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30177200</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,107 +3884,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1378100</v>
+      </c>
+      <c r="E81" s="3">
         <v>992600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1180200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1032100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1113400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>977600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>670400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>894300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>741400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>821600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>295800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>680800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>833000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1066400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E83" s="3">
         <v>94000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>102800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>125600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>122200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>124400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>132000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>128300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>136000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>136100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>123300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>115200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>122300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>129500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>117500</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16593700</v>
+      </c>
+      <c r="E89" s="3">
         <v>4953900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27215300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12124300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5609800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11458100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8917900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3053600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4130500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>675600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24001700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4244000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12177800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1577400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2083000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-96900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-148900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-272700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-132200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-189100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-311300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-60100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-242200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-76400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-146100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-84300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-83200</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-726400</v>
+      </c>
+      <c r="E94" s="3">
         <v>429500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1644100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2051200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1094700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>9067600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1570100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1560900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1185600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>554300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1476500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1977200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3122200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>10173400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>729900</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>599100</v>
+      </c>
+      <c r="E96" s="3">
         <v>594500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>484700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>579700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>381500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>696900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>108300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>92200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>876500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>100500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>103700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>449600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>104400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1120900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>95300</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +4799,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5464800</v>
+      </c>
+      <c r="E100" s="3">
         <v>12315300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>23009400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10603100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13986700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3998500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9721700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1156400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6883800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2639300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9113100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9562800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5956600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3561900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2906400</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-30000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-17600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>15700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-37900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-18000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>39200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>32500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>7700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>28900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>111100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>167900</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11880300</v>
+      </c>
+      <c r="E102" s="3">
         <v>17700700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5829500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>524700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9471600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6419000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-783500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-354000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1583400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3831300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13397400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15795200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3117000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12197100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4226900</v>
       </c>
     </row>
